--- a/jira_export_2026-10-28.xlsx
+++ b/jira_export_2026-10-28.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>64,342 €</t>
+          <t>65,637 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>19,807 €</t>
+          <t>20,628 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44,324 €</t>
+          <t>44,799 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2260,11 +2260,11 @@
       <c r="N21" s="12" t="n">
         <v>706.25</v>
       </c>
-      <c r="O21" s="16" t="n">
-        <v>353.125</v>
+      <c r="O21" s="12" t="n">
+        <v>918.125</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>117.71</v>
+        <v>306.04</v>
       </c>
     </row>
     <row r="22">
@@ -2676,11 +2676,11 @@
       <c r="N27" s="12" t="n">
         <v>427.5</v>
       </c>
-      <c r="O27" s="16" t="n">
-        <v>0</v>
+      <c r="O27" s="12" t="n">
+        <v>475</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>105.56</v>
       </c>
     </row>
     <row r="28">
@@ -2749,10 +2749,10 @@
         <v>2000</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>1340.325</v>
+        <v>1595.625</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>243.7</v>
+        <v>290.11</v>
       </c>
     </row>
     <row r="29">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
@@ -12409,10 +12409,10 @@
         <v>64820.36599999999</v>
       </c>
       <c r="O170" s="18" t="n">
-        <v>64341.832</v>
+        <v>65637.13200000001</v>
       </c>
       <c r="P170" s="18" t="n">
-        <v>208.35</v>
+        <v>212.55</v>
       </c>
     </row>
   </sheetData>
@@ -14134,10 +14134,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>463057</v>
+        <v>461762</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>187333</v>
+        <v>186038</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>275724</v>
@@ -14159,10 +14159,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>251714</v>
+        <v>250893</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69184</v>
+        <v>68364</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>182529</v>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>208243</v>
+        <v>207768</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>115049</v>
+        <v>114574</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>93194</v>

--- a/jira_export_2026-10-28.xlsx
+++ b/jira_export_2026-10-28.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>65,637 €</t>
+          <t>68,387 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>20,628 €</t>
+          <t>23,378 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
@@ -11327,10 +11327,10 @@
         <v>0</v>
       </c>
       <c r="O150" s="15" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P150" s="15" t="n">
-        <v>0</v>
+        <v>297.3</v>
       </c>
     </row>
     <row r="151">
@@ -12409,10 +12409,10 @@
         <v>64820.36599999999</v>
       </c>
       <c r="O170" s="18" t="n">
-        <v>65637.13200000001</v>
+        <v>68387.13200000001</v>
       </c>
       <c r="P170" s="18" t="n">
-        <v>212.55</v>
+        <v>221.45</v>
       </c>
     </row>
   </sheetData>
@@ -12594,7 +12594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -12620,7 +12620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 15 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 16 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -12685,22 +12685,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[VILLE D'AIGLE] - Ajout MATERIEL</t>
+          <t xml:space="preserve">[COMMUNE DE SALON DE PROVENCE] - Remplacement imprimante GEODP 1 </t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Ajout MATERIEL</t>
+          <t xml:space="preserve">Remplacement imprimante GEODP 1 </t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -12723,37 +12723,37 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36333</t>
+          <t>PDMDEP-36374</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>00184404</t>
+          <t>00184664</t>
         </is>
       </c>
       <c r="K5" s="12" t="n">
-        <v>815</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMME DE FECAMP] - Migration GEODP + mise en service paiement cb et 1 TPE </t>
+          <t>[VILLE D'AIGLE] - Ajout MATERIEL</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP + mise en service paiement cb et 1 TPE </t>
+          <t>Ajout MATERIEL</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H6" s="14" t="n">
@@ -12776,12 +12776,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36212</t>
+          <t>PDMDEP-36333</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>00176660</t>
+          <t>00184404</t>
         </is>
       </c>
       <c r="K6" s="15" t="n">
@@ -12791,22 +12791,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Acquisition et paramétrage 2 PAXA920 Pro </t>
+          <t xml:space="preserve">[COMME DE FECAMP] - Migration GEODP + mise en service paiement cb et 1 TPE </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acquisition et paramétrage 2 PAXA920 Pro </t>
+          <t xml:space="preserve">Migration GEODP + mise en service paiement cb et 1 TPE </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -12829,37 +12829,37 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35604</t>
+          <t>PDMDEP-36212</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00181048</t>
+          <t>00176660</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t xml:space="preserve">[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Acquisition et paramétrage 2 PAXA920 Pro </t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t xml:space="preserve">Acquisition et paramétrage 2 PAXA920 Pro </t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -12882,37 +12882,37 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35476</t>
+          <t>PDMDEP-35604</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00180644</t>
+          <t>00181048</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35227</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHAUNY</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35234</t>
+          <t>PDMDEP-35476</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>00179117</t>
+          <t>00180644</t>
         </is>
       </c>
       <c r="K9" s="12" t="n">
@@ -12950,22 +12950,22 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-35227</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>VILLE DE CHAUNY</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -12988,37 +12988,37 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34294</t>
+          <t>PDMDEP-35234</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00171435</t>
+          <t>00179117</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -13041,37 +13041,37 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34256</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>00171362</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K11" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H12" s="14" t="n">
@@ -13094,12 +13094,12 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34199</t>
+          <t>PDMDEP-34256</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>00171163</t>
+          <t>00171362</t>
         </is>
       </c>
       <c r="K12" s="15" t="n">
@@ -13109,22 +13109,22 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H13" s="11" t="n">
@@ -13147,37 +13147,37 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34199</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171163</t>
         </is>
       </c>
       <c r="K13" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -13200,37 +13200,37 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33848</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>00161104</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H15" s="11" t="n">
@@ -13253,37 +13253,37 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33692</t>
+          <t>PDMDEP-33848</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>00169320</t>
+          <t>00161104</t>
         </is>
       </c>
       <c r="K15" s="12" t="n">
-        <v>2445</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H16" s="14" t="n">
@@ -13306,37 +13306,37 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33156</t>
+          <t>PDMDEP-33692</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>00165721</t>
+          <t>00169320</t>
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>815</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -13359,37 +13359,37 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32200</t>
+          <t>PDMDEP-33156</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>00160783</t>
+          <t>00165721</t>
         </is>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -13412,37 +13412,37 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-32200</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00160783</t>
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31486</t>
+          <t>PDMDEP-31819</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>00157474</t>
+          <t>00159472</t>
         </is>
       </c>
       <c r="K19" s="12" t="n">
@@ -13478,22 +13478,75 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr"/>
-      <c r="D20" s="17" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr"/>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr"/>
-      <c r="I20" s="17" t="inlineStr"/>
-      <c r="J20" s="17" t="inlineStr"/>
-      <c r="K20" s="18" t="n">
-        <v>17115</v>
+      <c r="B21" s="17" t="inlineStr"/>
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="17" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="17" t="inlineStr"/>
+      <c r="J21" s="17" t="inlineStr"/>
+      <c r="K21" s="18" t="n">
+        <v>17565</v>
       </c>
     </row>
   </sheetData>
@@ -13514,6 +13567,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14134,10 +14188,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>461762</v>
+        <v>459012</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>186038</v>
+        <v>183288</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>275724</v>
@@ -14159,10 +14213,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>250893</v>
+        <v>248143</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>68364</v>
+        <v>65614</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>182529</v>

--- a/jira_export_2026-10-28.xlsx
+++ b/jira_export_2026-10-28.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>70,296 €</t>
+          <t>71,117 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>23,378 €</t>
+          <t>23,984 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,708 €</t>
+          <t>46,922 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4525,7 +4525,7 @@
         <v>1073.25</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>0</v>
+        <v>214.65</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -9688,28 +9688,26 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v/>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -9728,30 +9726,30 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>12</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="P126" s="15" t="n">
         <v>0</v>
@@ -9760,12 +9758,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9775,11 +9773,13 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
@@ -9793,49 +9793,49 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>10.5</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O127" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9868,54 +9868,54 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.75</v>
+        <v>10.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="15" t="n">
-        <v>0</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O128" s="16" t="n">
+        <v>2178.28</v>
       </c>
       <c r="P128" s="15" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9933,49 +9933,49 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>12.5</v>
+        <v>0.75</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="12" t="n">
-        <v>2497.125</v>
+        <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
-        <v>199.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10008,44 +10008,44 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.5</v>
+        <v>12.5</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>0</v>
+        <v>2497.125</v>
       </c>
       <c r="P130" s="15" t="n">
-        <v>0</v>
+        <v>199.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10078,23 +10078,23 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
         <v>15</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
@@ -10320,22 +10320,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22120</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD 29 ] FLUX WFS</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10348,27 +10348,35 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr"/>
-      <c r="M135" s="11" t="inlineStr"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10382,22 +10390,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10410,7 +10418,7 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr">
@@ -10420,25 +10428,17 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M136" s="14" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10452,12 +10452,12 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10485,28 +10485,28 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
@@ -10522,22 +10522,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10555,28 +10555,28 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N138" s="15" t="n">
@@ -10592,12 +10592,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10620,23 +10620,35 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10650,22 +10662,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10678,35 +10690,23 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10720,12 +10720,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10753,28 +10753,28 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N141" s="12" t="n">
@@ -10790,12 +10790,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10823,28 +10823,28 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N142" s="15" t="n">
@@ -10860,12 +10860,12 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
@@ -10875,13 +10875,11 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v/>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
@@ -10890,27 +10888,35 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10924,26 +10930,28 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E144" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
@@ -10962,14 +10970,14 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10986,22 +10994,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11019,7 +11027,7 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
@@ -11048,22 +11056,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11071,44 +11079,36 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M146" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
       <c r="N146" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="15" t="n">
@@ -11118,22 +11118,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
@@ -11151,34 +11151,34 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O147" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="12" t="n">
@@ -11188,22 +11188,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr">
@@ -11226,17 +11226,25 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K148" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L148" s="14" t="inlineStr"/>
-      <c r="M148" s="14" t="inlineStr"/>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11250,12 +11258,12 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -11265,7 +11273,7 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11288,14 +11296,14 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11312,22 +11320,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11350,14 +11358,14 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11374,22 +11382,22 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11412,14 +11420,14 @@
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11436,12 +11444,12 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
@@ -11451,7 +11459,7 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11469,19 +11477,19 @@
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L152" s="14" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -11498,12 +11506,12 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
@@ -11513,7 +11521,7 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11526,35 +11534,27 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11568,22 +11568,22 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11596,23 +11596,35 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H154" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L154" s="14" t="inlineStr"/>
-      <c r="M154" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N154" s="15" t="n">
         <v>0</v>
       </c>
@@ -11626,12 +11638,12 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
@@ -11641,7 +11653,7 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11657,61 +11669,49 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H155" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>3.75</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="12" t="n">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="P155" s="12" t="n">
-        <v>297.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E156" s="14" t="n">
@@ -11724,62 +11724,68 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H156" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>2.5</v>
+        <v>9.25</v>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M156" s="14" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="15" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P156" s="15" t="n">
-        <v>0</v>
+        <v>297.3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C157" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v/>
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
@@ -11788,27 +11794,31 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H157" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N157" s="12" t="n">
         <v>0</v>
       </c>
@@ -11822,21 +11832,25 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11844,20 +11858,24 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H158" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>0.25</v>
+        <v>2.75</v>
       </c>
       <c r="L158" s="14" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -11874,46 +11892,50 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="11" t="inlineStr"/>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
       <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr"/>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr"/>
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="12" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P159" s="12" t="n">
         <v>0</v>
@@ -11922,50 +11944,46 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
-      <c r="D160" s="14" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VALENCAY</t>
-        </is>
-      </c>
+      <c r="D160" s="14" t="inlineStr"/>
       <c r="E160" s="14" t="inlineStr"/>
-      <c r="F160" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="F160" s="14" t="inlineStr"/>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P160" s="15" t="n">
         <v>0</v>
@@ -11974,18 +11992,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -12002,7 +12020,7 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
@@ -12026,18 +12044,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12048,56 +12066,48 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K162" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L162" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M162" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
       <c r="N162" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O162" s="16" t="n">
-        <v>350</v>
+        <v>0</v>
+      </c>
+      <c r="O162" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P162" s="15" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12108,13 +12118,13 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
@@ -12123,33 +12133,41 @@
       <c r="K163" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr"/>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="12" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O163" s="16" t="n">
+        <v>350</v>
       </c>
       <c r="P163" s="12" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12160,31 +12178,23 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M164" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="14" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12198,18 +12208,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12220,23 +12230,31 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12250,18 +12268,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12278,14 +12296,14 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L166" s="14" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -12302,18 +12320,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12330,14 +12348,14 @@
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="L167" s="11" t="inlineStr"/>
       <c r="M167" s="11" t="inlineStr"/>
@@ -12354,18 +12372,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12376,31 +12394,23 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L168" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M168" s="14" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L168" s="14" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
       <c r="N168" s="15" t="n">
         <v>0</v>
       </c>
@@ -12414,18 +12424,18 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12442,23 +12452,23 @@
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M169" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N169" s="12" t="n">
@@ -12474,18 +12484,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12496,23 +12506,31 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr"/>
-      <c r="M170" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N170" s="15" t="n">
         <v>0</v>
       </c>
@@ -12526,18 +12544,18 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12548,31 +12566,23 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L171" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L171" s="11" t="inlineStr"/>
+      <c r="M171" s="11" t="inlineStr"/>
       <c r="N171" s="12" t="n">
         <v>0</v>
       </c>
@@ -12586,18 +12596,18 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr"/>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr"/>
@@ -12608,23 +12618,31 @@
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J172" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K172" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L172" s="14" t="inlineStr"/>
-      <c r="M172" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L172" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-30236</t>
+        </is>
+      </c>
+      <c r="M172" s="14" t="inlineStr">
+        <is>
+          <t>00152992</t>
+        </is>
+      </c>
       <c r="N172" s="15" t="n">
         <v>0</v>
       </c>
@@ -12638,18 +12656,18 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr"/>
@@ -12660,31 +12678,23 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J173" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L173" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L173" s="11" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr"/>
       <c r="N173" s="12" t="n">
         <v>0</v>
       </c>
@@ -12698,18 +12708,18 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C174" s="14" t="inlineStr"/>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr"/>
@@ -12720,59 +12730,119 @@
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
       <c r="I174" s="14" t="inlineStr">
         <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K174" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L174" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M174" s="14" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
+      <c r="N174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr"/>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr"/>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr"/>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
           <t>10/06/2025</t>
         </is>
       </c>
-      <c r="J174" s="14" t="n">
+      <c r="J175" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="K174" s="14" t="n">
+      <c r="K175" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="L174" s="14" t="inlineStr"/>
-      <c r="M174" s="14" t="inlineStr"/>
-      <c r="N174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="17" t="inlineStr">
+      <c r="L175" s="11" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr"/>
+      <c r="N175" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B175" s="17" t="inlineStr"/>
-      <c r="C175" s="17" t="inlineStr"/>
-      <c r="D175" s="17" t="inlineStr"/>
-      <c r="E175" s="17" t="inlineStr"/>
-      <c r="F175" s="17" t="inlineStr"/>
-      <c r="G175" s="17" t="inlineStr"/>
-      <c r="H175" s="17" t="inlineStr"/>
-      <c r="I175" s="17" t="inlineStr"/>
-      <c r="J175" s="17" t="inlineStr"/>
-      <c r="K175" s="17" t="inlineStr"/>
-      <c r="L175" s="17" t="inlineStr"/>
-      <c r="M175" s="17" t="inlineStr"/>
-      <c r="N175" s="18" t="n">
-        <v>64820.36599999999</v>
-      </c>
-      <c r="O175" s="18" t="n">
-        <v>70296.092</v>
-      </c>
-      <c r="P175" s="18" t="n">
-        <v>227.27</v>
+      <c r="B176" s="17" t="inlineStr"/>
+      <c r="C176" s="17" t="inlineStr"/>
+      <c r="D176" s="17" t="inlineStr"/>
+      <c r="E176" s="17" t="inlineStr"/>
+      <c r="F176" s="17" t="inlineStr"/>
+      <c r="G176" s="17" t="inlineStr"/>
+      <c r="H176" s="17" t="inlineStr"/>
+      <c r="I176" s="17" t="inlineStr"/>
+      <c r="J176" s="17" t="inlineStr"/>
+      <c r="K176" s="17" t="inlineStr"/>
+      <c r="L176" s="17" t="inlineStr"/>
+      <c r="M176" s="17" t="inlineStr"/>
+      <c r="N176" s="18" t="n">
+        <v>65426.36599999999</v>
+      </c>
+      <c r="O176" s="18" t="n">
+        <v>71116.742</v>
+      </c>
+      <c r="P176" s="18" t="n">
+        <v>229.92</v>
       </c>
     </row>
   </sheetData>
@@ -12948,6 +13018,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14653,10 +14724,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>478925</v>
+        <v>478105</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>200165</v>
+        <v>199344</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>278760</v>
@@ -14678,10 +14749,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>248143</v>
+        <v>247537</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>65614</v>
+        <v>65008</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>182529</v>
@@ -14703,10 +14774,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>227682</v>
+        <v>227467</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>131451</v>
+        <v>131236</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>96231</v>

--- a/jira_export_2026-10-28.xlsx
+++ b/jira_export_2026-10-28.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>71,117 €</t>
+          <t>71,994 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,922 €</t>
+          <t>47,800 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -3397,10 +3397,10 @@
         <v>1068.45</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>3331.05</v>
+        <v>3582.45</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>666.21</v>
+        <v>716.49</v>
       </c>
     </row>
     <row r="38">
@@ -3957,7 +3957,7 @@
         <v>250.5</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>250.5</v>
+        <v>876.75</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -12839,10 +12839,10 @@
         <v>65426.36599999999</v>
       </c>
       <c r="O176" s="18" t="n">
-        <v>71116.742</v>
+        <v>71994.39199999999</v>
       </c>
       <c r="P176" s="18" t="n">
-        <v>229.92</v>
+        <v>232.76</v>
       </c>
     </row>
   </sheetData>
@@ -14724,19 +14724,19 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>478105</v>
+        <v>477227</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>199344</v>
+        <v>198718</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>278760</v>
+        <v>278509</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>219787</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>16560</v>
+        <v>16308</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>17943</v>
@@ -14774,19 +14774,19 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>227467</v>
+        <v>226590</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>131236</v>
+        <v>130610</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>96231</v>
+        <v>95979</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>56470</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>7385</v>
+        <v>7133</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>
@@ -16025,12 +16025,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -16046,7 +16046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 clôture(s) : 11 projet(s), 0 rework</t>
+          <t>12 clôture(s) : 12 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -16176,17 +16176,17 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34000</t>
+          <t>PDMDEP-33712</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+          <t>[COMMUNE DE BONNIERES SUR SEINE] - ABONNEMENT DATA M2M</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DE BONNIERES SUR SEINE</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -16206,17 +16206,17 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34000</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -16236,17 +16236,17 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -16266,17 +16266,17 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -16290,23 +16290,23 @@
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35261</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -16326,17 +16326,17 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-35261</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>[VILLE D'AIGLE] - Ajout MATERIEL</t>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -16350,28 +16350,28 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vi</t>
+          <t>[VILLE D'AIGLE] - Ajout MATERIEL</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -16380,65 +16380,95 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-30062</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vi</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Saint-Dizier</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35840</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>[COMMUNE DE SETE] - Publication des actes</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE SETE</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n">
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-28.xlsx
+++ b/jira_export_2026-10-28.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>489 h</t>
+          <t>504 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -9663,7 +9663,7 @@
         <v>11</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>12</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>2178.28</v>
       </c>
       <c r="P128" s="15" t="n">
-        <v>207.46</v>
+        <v>181.52</v>
       </c>
     </row>
     <row r="129">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -12842,7 +12842,7 @@
         <v>71994.39199999999</v>
       </c>
       <c r="P176" s="18" t="n">
-        <v>232.76</v>
+        <v>230.52</v>
       </c>
     </row>
   </sheetData>
@@ -13030,7 +13030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13056,7 +13056,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 18 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 20 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13484,22 +13484,22 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -13522,37 +13522,37 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34294</t>
+          <t>PDMDEP-35137</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>00171435</t>
+          <t>00178822</t>
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[COMMUNE DE LA FLÈCHE] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34256</t>
+          <t>PDMDEP-34464</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>00171362</t>
+          <t>00172595</t>
         </is>
       </c>
       <c r="K13" s="12" t="n">
@@ -13590,22 +13590,22 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H14" s="14" t="n">
@@ -13628,37 +13628,37 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34199</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>00171163</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -13681,37 +13681,37 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34256</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171362</t>
         </is>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H16" s="14" t="n">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33848</t>
+          <t>PDMDEP-34199</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>00161104</t>
+          <t>00171163</t>
         </is>
       </c>
       <c r="K16" s="15" t="n">
@@ -13749,22 +13749,22 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H17" s="11" t="n">
@@ -13787,37 +13787,37 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33692</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>00169320</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K17" s="12" t="n">
-        <v>2445</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33214</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CESTAS] - Commande d'un Pax + M2M pour remplacer le smartphone</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CESTAS</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Commande d'un Pax + M2M pour remplacer le smartphone</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H18" s="14" t="n">
@@ -13840,12 +13840,12 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33220</t>
+          <t>PDMDEP-33848</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>00166588</t>
+          <t>00161104</t>
         </is>
       </c>
       <c r="K18" s="15" t="n">
@@ -13855,22 +13855,22 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H19" s="11" t="n">
@@ -13893,37 +13893,37 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33156</t>
+          <t>PDMDEP-33692</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>00165721</t>
+          <t>00169320</t>
         </is>
       </c>
       <c r="K19" s="12" t="n">
-        <v>815</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-33214</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE CESTAS] - Commande d'un Pax + M2M pour remplacer le smartphone</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE CESTAS</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Commande d'un Pax + M2M pour remplacer le smartphone</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H20" s="14" t="n">
@@ -13946,37 +13946,37 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32200</t>
+          <t>PDMDEP-33220</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>00160783</t>
+          <t>00166588</t>
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-33156</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00165721</t>
         </is>
       </c>
       <c r="K21" s="12" t="n">
@@ -14014,73 +14014,179 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-32193</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTAUBAN</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32200</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>00160783</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-31812</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE PROVINS</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31819</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>00159472</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
           <t>PDMDEP-31479</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Migration vers GeoDP V2</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="H24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-31486</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>00157474</t>
         </is>
       </c>
-      <c r="K22" s="15" t="n">
+      <c r="K24" s="15" t="n">
         <v>815</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr"/>
-      <c r="D23" s="17" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr"/>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr"/>
-      <c r="I23" s="17" t="inlineStr"/>
-      <c r="J23" s="17" t="inlineStr"/>
-      <c r="K23" s="18" t="n">
-        <v>18380</v>
+      <c r="B25" s="17" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr"/>
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="17" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
+      <c r="I25" s="17" t="inlineStr"/>
+      <c r="J25" s="17" t="inlineStr"/>
+      <c r="K25" s="18" t="n">
+        <v>20010</v>
       </c>
     </row>
   </sheetData>
@@ -14104,6 +14210,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14578,7 +14686,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>25.25</v>
@@ -14587,7 +14695,7 @@
         <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>235.33</v>
+        <v>238.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>40</v>
@@ -14597,7 +14705,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14747,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>135.83</v>
+        <v>147.08</v>
       </c>
     </row>
   </sheetData>
@@ -14803,7 +14911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14827,7 +14935,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 24 commande(s)</t>
+          <t>Épics créées ce mois — 27 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14882,22 +14990,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36757</t>
+          <t>PDMDEP-36459</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36748</t>
+          <t>PDMDEP-36453</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CHATILLON SUR CHALARONNE</t>
+          <t xml:space="preserve">COMMUNE DE EVREUX </t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14907,7 +15015,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -14917,11 +15025,11 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00185435</t>
+          <t>00184982</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
     </row>
     <row r="6">
@@ -15017,22 +15125,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -15042,7 +15150,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -15052,32 +15160,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>985</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36474</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36465</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -15097,32 +15205,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00185032</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1800</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36459</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36453</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE EVREUX </t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -15142,32 +15250,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00184982</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>895</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36474</t>
+          <t>PDMDEP-36519</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36465</t>
+          <t>PDMDEP-36510</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE LANCON PROVENCE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -15187,32 +15295,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00185032</t>
+          <t>00185247</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>4685</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36387</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36381</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRIANCON</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -15232,32 +15340,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00184667</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36581</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36572</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>MAIRIE EYMET</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -15267,7 +15375,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -15277,32 +15385,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00185751</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>2500</v>
+        <v>1667.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36581</t>
+          <t>PDMDEP-36614</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36572</t>
+          <t>PDMDEP-36608</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE EYMET</t>
+          <t>COMMUNE DE MARSEILLAN</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -15312,7 +15420,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -15322,32 +15430,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00185751</t>
+          <t>00185893</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>1667.5</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36614</t>
+          <t>PDMDEP-36645</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36608</t>
+          <t>PDMDEP-36639</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MARSEILLAN</t>
+          <t>Ville de Fleury  Les Aubrais</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -15367,22 +15475,22 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00185893</t>
+          <t>00186007</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>6800</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36645</t>
+          <t>PDMDEP-36659</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36639</t>
+          <t>PDMDEP-36653</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -15392,7 +15500,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Ville de Fleury  Les Aubrais</t>
+          <t>Commune de Dreux</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -15402,7 +15510,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -15412,32 +15520,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00186007</t>
+          <t>00186097</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>3250</v>
+        <v>8805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36659</t>
+          <t>PDMDEP-36746</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36653</t>
+          <t>PDMDEP-36309</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Commune de Dreux</t>
+          <t>COMMUNE D OYONNAX</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -15447,42 +15555,34 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>00186097</t>
-        </is>
-      </c>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
       <c r="I17" s="25" t="n">
-        <v>8805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36746</t>
+          <t>PDMDEP-36757</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36309</t>
+          <t>PDMDEP-36748</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D OYONNAX</t>
+          <t>MAIRIE DE CHATILLON SUR CHALARONNE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -15492,11 +15592,19 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr"/>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>00185435</t>
+        </is>
+      </c>
       <c r="I18" s="26" t="n">
         <v>0</v>
       </c>
@@ -15504,22 +15612,22 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36519</t>
+          <t>PDMDEP-36771</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36510</t>
+          <t>PDMDEP-36767</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LANCON PROVENCE</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -15529,7 +15637,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -15539,11 +15647,11 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00185247</t>
+          <t>00186190</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15594,32 +15702,32 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36387</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36381</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE DE BRIANCON</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -15629,32 +15737,32 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00184667</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36439</t>
+          <t>PDMDEP-36197</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36435</t>
+          <t>PDMDEP-36190</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANGERS</t>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -15664,7 +15772,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -15674,32 +15782,32 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00184863</t>
+          <t>00183894</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>4000</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36427</t>
+          <t>PDMDEP-36781</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36776</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t xml:space="preserve">Ville de Chartres </t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -15719,17 +15827,17 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>00184846</t>
+          <t>00186194</t>
         </is>
       </c>
       <c r="I23" s="25" t="n">
-        <v>3575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36428</t>
+          <t>PDMDEP-36427</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -15764,32 +15872,32 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>00184334</t>
+          <t>00184846</t>
         </is>
       </c>
       <c r="I24" s="26" t="n">
-        <v>0</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36497</t>
+          <t>PDMDEP-36428</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36493</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE SEINE ET MARNE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -15809,32 +15917,32 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>00185186</t>
+          <t>00184334</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36555</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36549</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -15854,32 +15962,32 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>00185556</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I26" s="26" t="n">
-        <v>750</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36402</t>
+          <t>PDMDEP-36497</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36398</t>
+          <t>PDMDEP-36493</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+          <t>DEPARTEMENT DE SEINE ET MARNE</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -15899,118 +16007,253 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>00184748</t>
+          <t>00185186</t>
         </is>
       </c>
       <c r="I27" s="25" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36555</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36549</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>00185556</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36780</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36776</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville de Chartres </t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>00186195</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36402</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36398</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>00184748</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I31" s="25" t="n">
         <v>2310</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>24 commande(s)</t>
-        </is>
-      </c>
-      <c r="I29" s="24" t="n">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>27 commande(s)</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="n">
         <v>50290</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>dont Littéralis</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>8 commande(s)</t>
-        </is>
-      </c>
-      <c r="I30" s="24" t="n">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>10 commande(s)</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="n">
         <v>16853</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>dont GEODP</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>16 commande(s)</t>
-        </is>
-      </c>
-      <c r="I31" s="24" t="n">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>17 commande(s)</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="n">
         <v>33438</v>
       </c>
     </row>
